--- a/artfynd/A 24880-2026 artfynd.xlsx
+++ b/artfynd/A 24880-2026 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>134084648</v>
       </c>
       <c r="B5" t="n">
-        <v>4776</v>
+        <v>4777</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 24880-2026 artfynd.xlsx
+++ b/artfynd/A 24880-2026 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>134084648</v>
       </c>
       <c r="B5" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
